--- a/VTU/usn_list.xlsx
+++ b/VTU/usn_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\india\Desktop\VTU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC853C42-2F7C-4F92-9053-B3A32575FA7C}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07ADF4B-1BD7-4C15-9EA6-513F7E5AC576}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D3C98C4-02F0-4FB4-9D88-793BC642E170}"/>
+    <workbookView xWindow="6315" yWindow="1965" windowWidth="8760" windowHeight="9030" xr2:uid="{3D3C98C4-02F0-4FB4-9D88-793BC642E170}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>USN</t>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t>1AM22AI003</t>
-  </si>
-  <si>
-    <t>1AM22AI004</t>
   </si>
 </sst>
 </file>
@@ -402,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75035D5B-D679-4EC4-BC71-1582A31A3314}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
@@ -428,11 +425,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
